--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$60</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2120" uniqueCount="409">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -823,208 +823,13 @@
     <t>If the use case requires  BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
   </si>
   <si>
     <t>SPM-8 and SPM-9</t>
-  </si>
-  <si>
-    <t>Specimen.collection.bodySite.id</t>
-  </si>
-  <si>
-    <t>Specimen.collection.bodySite.extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Specimen.collection.bodySite.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>Specimen.collection.bodySite.coding.id</t>
-  </si>
-  <si>
-    <t>Specimen.collection.bodySite.coding.extension</t>
-  </si>
-  <si>
-    <t>Specimen.collection.bodySite.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>Specimen.collection.bodySite.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>Specimen.collection.bodySite.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>Specimen.collection.bodySite.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>Specimen.collection.bodySite.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>Specimen.collection.bodySite.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>Specimen.collection.fastingStatus[x]</t>
@@ -1116,9 +921,44 @@
     <t>Specimen.processing.procedure.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>Specimen.processing.procedure.coding</t>
   </si>
   <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
     <t>Specimen.processing.procedure.coding.id</t>
   </si>
   <si>
@@ -1128,22 +968,140 @@
     <t>Specimen.processing.procedure.coding.system</t>
   </si>
   <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
     <t>Specimen.processing.procedure.coding.version</t>
   </si>
   <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
     <t>Specimen.processing.procedure.coding.code</t>
   </si>
   <si>
     <t>Acte de prélèvement</t>
   </si>
   <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
     <t>Specimen.processing.procedure.coding.display</t>
   </si>
   <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
     <t>Specimen.processing.procedure.coding.userSelected</t>
   </si>
   <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
     <t>Specimen.processing.procedure.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>Specimen.processing.additive</t>
@@ -1646,7 +1604,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM71"/>
+  <dimension ref="A1:AM60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.6953125" customWidth="true" bestFit="true"/>
@@ -1673,7 +1631,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="49.63671875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="48.99609375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="52.27734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -4735,13 +4693,11 @@
         <v>76</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y28" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y28" s="2"/>
+      <c r="Z28" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>76</v>
@@ -4774,21 +4730,21 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>261</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4808,19 +4764,23 @@
         <v>76</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>209</v>
+        <v>262</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>210</v>
+        <v>263</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>76</v>
       </c>
@@ -4844,13 +4804,13 @@
         <v>76</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>76</v>
+        <v>267</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>76</v>
+        <v>268</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>76</v>
@@ -4868,7 +4828,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4880,28 +4840,28 @@
         <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>213</v>
+        <v>76</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>76</v>
+        <v>269</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4920,17 +4880,15 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>132</v>
+        <v>271</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>76</v>
@@ -4967,19 +4925,19 @@
         <v>76</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>264</v>
+        <v>76</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>265</v>
+        <v>76</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>266</v>
+        <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>216</v>
+        <v>270</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4991,10 +4949,10 @@
         <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>213</v>
+        <v>273</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>76</v>
@@ -5005,10 +4963,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5016,7 +4974,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>85</v>
@@ -5028,23 +4986,19 @@
         <v>76</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>268</v>
+        <v>209</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>269</v>
+        <v>210</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>76</v>
       </c>
@@ -5092,47 +5046,47 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>273</v>
+        <v>212</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>274</v>
+        <v>213</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>275</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>76</v>
@@ -5144,15 +5098,17 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>209</v>
+        <v>131</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>210</v>
+        <v>132</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -5201,19 +5157,19 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>213</v>
@@ -5227,14 +5183,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>130</v>
+        <v>218</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5247,24 +5203,26 @@
         <v>76</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>131</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>132</v>
+        <v>219</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="O33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>76</v>
       </c>
@@ -5300,19 +5258,19 @@
         <v>76</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>264</v>
+        <v>76</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>265</v>
+        <v>76</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>266</v>
+        <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5327,7 +5285,7 @@
         <v>136</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>213</v>
+        <v>128</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>76</v>
@@ -5338,10 +5296,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5361,23 +5319,19 @@
         <v>76</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>99</v>
+        <v>209</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>282</v>
-      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>76</v>
       </c>
@@ -5386,7 +5340,7 @@
         <v>76</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>283</v>
+        <v>76</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>76</v>
@@ -5425,7 +5379,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5440,21 +5394,21 @@
         <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>286</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5474,20 +5428,18 @@
         <v>76</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>209</v>
+        <v>165</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>76</v>
@@ -5512,13 +5464,13 @@
         <v>76</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>76</v>
+        <v>249</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>76</v>
+        <v>284</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>76</v>
+        <v>285</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>76</v>
@@ -5536,7 +5488,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5551,21 +5503,21 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>292</v>
+        <v>171</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>293</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5585,21 +5537,19 @@
         <v>76</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>105</v>
+        <v>209</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>295</v>
+        <v>210</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>296</v>
+        <v>211</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>297</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>76</v>
       </c>
@@ -5647,7 +5597,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>298</v>
+        <v>212</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5659,35 +5609,35 @@
         <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>299</v>
+        <v>213</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>300</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>76</v>
@@ -5696,21 +5646,21 @@
         <v>76</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>209</v>
+        <v>131</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>302</v>
+        <v>132</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>76</v>
       </c>
@@ -5746,48 +5696,48 @@
         <v>76</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>76</v>
+        <v>288</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>76</v>
+        <v>289</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>76</v>
+        <v>290</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>305</v>
+        <v>216</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>306</v>
+        <v>213</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>307</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5798,7 +5748,7 @@
         <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>76</v>
@@ -5810,19 +5760,19 @@
         <v>86</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>76</v>
@@ -5871,13 +5821,13 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>76</v>
@@ -5886,21 +5836,21 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>316</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5920,23 +5870,19 @@
         <v>76</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>209</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>318</v>
+        <v>210</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>76</v>
       </c>
@@ -5984,7 +5930,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>322</v>
+        <v>212</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5996,35 +5942,35 @@
         <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>323</v>
+        <v>213</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>324</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>76</v>
@@ -6033,23 +5979,21 @@
         <v>76</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>326</v>
+        <v>131</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>327</v>
+        <v>132</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>328</v>
+        <v>215</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>76</v>
       </c>
@@ -6073,60 +6017,60 @@
         <v>76</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>169</v>
+        <v>76</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>331</v>
+        <v>76</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>332</v>
+        <v>76</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>76</v>
+        <v>288</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>76</v>
+        <v>289</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>76</v>
+        <v>290</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>325</v>
+        <v>216</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>76</v>
+        <v>213</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>333</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>334</v>
+        <v>302</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>334</v>
+        <v>302</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6137,7 +6081,7 @@
         <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>76</v>
@@ -6146,19 +6090,23 @@
         <v>76</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>203</v>
+        <v>99</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>335</v>
+        <v>303</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>76</v>
       </c>
@@ -6206,13 +6154,13 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>334</v>
+        <v>307</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>76</v>
@@ -6221,21 +6169,21 @@
         <v>97</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>337</v>
+        <v>308</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>76</v>
+        <v>309</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>338</v>
+        <v>310</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>338</v>
+        <v>310</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6255,18 +6203,20 @@
         <v>76</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>209</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>210</v>
+        <v>311</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>76</v>
@@ -6315,7 +6265,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>212</v>
+        <v>314</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6327,58 +6277,58 @@
         <v>76</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>213</v>
+        <v>315</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>76</v>
+        <v>316</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>132</v>
+        <v>318</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>76</v>
       </c>
@@ -6426,71 +6376,69 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>216</v>
+        <v>321</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>213</v>
+        <v>322</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>76</v>
+        <v>323</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>218</v>
+        <v>76</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>131</v>
+        <v>209</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>219</v>
+        <v>325</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>140</v>
+        <v>327</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>76</v>
@@ -6539,36 +6487,36 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>221</v>
+        <v>328</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>128</v>
+        <v>329</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>76</v>
+        <v>330</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6588,19 +6536,23 @@
         <v>76</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>209</v>
+        <v>332</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>76</v>
       </c>
@@ -6648,7 +6600,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6663,21 +6615,21 @@
         <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>76</v>
+        <v>339</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6697,19 +6649,23 @@
         <v>76</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>165</v>
+        <v>209</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
       </c>
@@ -6733,13 +6689,13 @@
         <v>76</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>249</v>
+        <v>76</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>348</v>
+        <v>76</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>349</v>
+        <v>76</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>76</v>
@@ -6772,21 +6728,21 @@
         <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>171</v>
+        <v>346</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>76</v>
+        <v>347</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6797,10 +6753,10 @@
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>76</v>
@@ -6809,13 +6765,13 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>209</v>
+        <v>349</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>210</v>
+        <v>350</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>211</v>
+        <v>351</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6866,47 +6822,47 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>212</v>
+        <v>348</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>213</v>
+        <v>352</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>76</v>
+        <v>353</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>76</v>
@@ -6918,17 +6874,15 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>131</v>
+        <v>230</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>132</v>
+        <v>355</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -6965,34 +6919,34 @@
         <v>76</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>264</v>
+        <v>76</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>265</v>
+        <v>76</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>266</v>
+        <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>216</v>
+        <v>354</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>76</v>
@@ -7001,12 +6955,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7020,29 +6974,25 @@
         <v>78</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>269</v>
+        <v>358</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>76</v>
       </c>
@@ -7090,7 +7040,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>273</v>
+        <v>357</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7105,21 +7055,21 @@
         <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>274</v>
+        <v>360</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>275</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7225,10 +7175,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7298,16 +7248,16 @@
         <v>76</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>264</v>
+        <v>76</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>265</v>
+        <v>76</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>266</v>
+        <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>216</v>
@@ -7336,45 +7286,45 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>76</v>
+        <v>218</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>279</v>
+        <v>219</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>281</v>
+        <v>134</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>282</v>
+        <v>140</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>76</v>
@@ -7423,36 +7373,36 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>284</v>
+        <v>221</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>285</v>
+        <v>128</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>286</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7463,7 +7413,7 @@
         <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>76</v>
@@ -7475,17 +7425,15 @@
         <v>86</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>209</v>
+        <v>143</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>288</v>
+        <v>365</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>76</v>
@@ -7534,13 +7482,13 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>291</v>
+        <v>364</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>76</v>
@@ -7549,21 +7497,21 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>292</v>
+        <v>146</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>293</v>
+        <v>367</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7571,33 +7519,31 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>105</v>
+        <v>209</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>296</v>
+        <v>370</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>297</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>76</v>
       </c>
@@ -7645,7 +7591,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>298</v>
+        <v>368</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7660,21 +7606,21 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>299</v>
+        <v>371</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>300</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7682,33 +7628,31 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>209</v>
+        <v>165</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>302</v>
+        <v>373</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>303</v>
+        <v>374</v>
       </c>
       <c r="N55" s="2"/>
-      <c r="O55" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>76</v>
       </c>
@@ -7732,13 +7676,13 @@
         <v>76</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>76</v>
+        <v>249</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>76</v>
+        <v>375</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>76</v>
+        <v>376</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>76</v>
@@ -7756,7 +7700,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>305</v>
+        <v>372</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7771,21 +7715,21 @@
         <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>306</v>
+        <v>171</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>307</v>
+        <v>377</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7805,23 +7749,19 @@
         <v>76</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>310</v>
+        <v>379</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>76</v>
       </c>
@@ -7869,7 +7809,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -7884,21 +7824,21 @@
         <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>315</v>
+        <v>381</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>316</v>
+        <v>382</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7918,23 +7858,19 @@
         <v>76</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>318</v>
+        <v>384</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>76</v>
       </c>
@@ -7982,7 +7918,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>322</v>
+        <v>383</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -7997,21 +7933,21 @@
         <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>323</v>
+        <v>386</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>324</v>
+        <v>387</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8022,10 +7958,10 @@
         <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>76</v>
@@ -8034,13 +7970,13 @@
         <v>76</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8067,13 +8003,13 @@
         <v>76</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>76</v>
+        <v>249</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>76</v>
+        <v>392</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>76</v>
@@ -8091,13 +8027,13 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>76</v>
@@ -8106,21 +8042,21 @@
         <v>97</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>367</v>
+        <v>395</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8131,7 +8067,7 @@
         <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>76</v>
@@ -8140,19 +8076,23 @@
         <v>76</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>230</v>
+        <v>165</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>76</v>
       </c>
@@ -8176,13 +8116,13 @@
         <v>76</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>76</v>
+        <v>401</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>76</v>
+        <v>402</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>76</v>
@@ -8200,13 +8140,13 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>76</v>
@@ -8215,21 +8155,21 @@
         <v>97</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>233</v>
+        <v>76</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>76</v>
+        <v>403</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8243,7 +8183,7 @@
         <v>78</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>76</v>
@@ -8252,13 +8192,13 @@
         <v>76</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>203</v>
+        <v>405</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>372</v>
+        <v>50</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>373</v>
+        <v>406</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8309,7 +8249,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8324,1226 +8264,17 @@
         <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>374</v>
+        <v>407</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
-      <c r="P66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK69" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="70" hidden="true">
-      <c r="A70" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="P70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>422</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM71">
+  <autoFilter ref="A1:AM60">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9553,7 +8284,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI70">
+  <conditionalFormatting sqref="A2:AI59">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/main/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
